--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>여성전용PT 핏투핏 송도점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>waterfallbody@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1458-9510</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 연수구 아트센터대로 87 401동 2층 210호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness/</t>
+          <t>https://blog.naver.com/waterfallbody</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdg5hky</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1355</v>
+        <v>137</v>
       </c>
       <c r="Q2" t="n">
-        <v>920</v>
+        <v>780</v>
       </c>
       <c r="R2" t="n">
-        <v>2275</v>
+        <v>917</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1851119903</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1851119903</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>프롬바디PT&amp;필라테스 인천대입구역점</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>from-body@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1425-0923</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크 102동 324호</t>
+          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://frombody.kr</t>
+          <t>https://www.instagram.com/resortfitness/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>291</v>
+        <v>1358</v>
       </c>
       <c r="Q3" t="n">
-        <v>1538</v>
+        <v>920</v>
       </c>
       <c r="R3" t="n">
-        <v>1829</v>
+        <v>2278</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1472986584</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472986584</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mk22</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -812,10 +824,10 @@
         <v>315</v>
       </c>
       <c r="Q4" t="n">
-        <v>1808</v>
+        <v>1816</v>
       </c>
       <c r="R4" t="n">
-        <v>2123</v>
+        <v>2131</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피지컬랩 송도PT</t>
+          <t>프롬바디PT&amp;필라테스 인천대입구역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>maxyh7@naver.com</t>
+          <t>from-body@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1332-2194</t>
+          <t>0507-1425-0923</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 테크노파크로111번길 11 시카고 타워 502호</t>
+          <t>인천 연수구 하모니로138번길 11 송도캐슬센트럴파크 102동 324호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/maxyh7/222056811037</t>
+          <t>https://frombody.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ofx5</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>183</v>
+        <v>291</v>
       </c>
       <c r="Q5" t="n">
-        <v>546</v>
+        <v>1543</v>
       </c>
       <c r="R5" t="n">
-        <v>729</v>
+        <v>1834</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1826127652</t>
+          <t>1472986584</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1826127652</t>
+          <t>https://m.place.naver.com/place/1472986584</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
+          <t>인천 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wual9v3</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1000,10 +1020,10 @@
         <v>57</v>
       </c>
       <c r="Q6" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="R6" t="n">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1034,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>더피티짐 헬스&amp;PT 글로벌캠퍼스점</t>
+          <t>매드볼릭 PT 헬스장 송도</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kyu0000000@naver.com</t>
+          <t>madbolic-songdo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1320-3080</t>
+          <t>0507-1352-6741</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도문화로28번길 28 글로벌캠퍼스푸르지오상가 202동 2층 208-210호</t>
+          <t>인천 연수구 테크노파크로111번길 11 시카고타워 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://thepit.creatorlink.net</t>
+          <t>https://blog.naver.com/madbolic-songdo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,18 +1091,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46104</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>334</v>
+        <v>559</v>
       </c>
       <c r="Q7" t="n">
-        <v>700</v>
+        <v>1242</v>
       </c>
       <c r="R7" t="n">
-        <v>1034</v>
+        <v>1801</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1189916238</t>
+          <t>1206099126</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189916238</t>
+          <t>https://m.place.naver.com/place/1206099126</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FWC스포츠센터</t>
+          <t>더피티짐 헬스&amp;PT 글로벌캠퍼스점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fwcsports@naver.com</t>
+          <t>kyu0000000@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1360-7005</t>
+          <t>0507-1320-3080</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
+          <t>인천 연수구 송도문화로28번길 28 글로벌캠퍼스푸르지오상가 202동 2층 208-210호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.fwcsongdo.com/</t>
+          <t>https://thepit.creatorlink.net</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,7 +1184,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1175,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4qg2m</t>
+          <t>https://talk.naver.com/ct/w4dk13</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>208</v>
+        <v>334</v>
       </c>
       <c r="Q8" t="n">
-        <v>643</v>
+        <v>700</v>
       </c>
       <c r="R8" t="n">
-        <v>851</v>
+        <v>1034</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>34249321</t>
+          <t>1189916238</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34249321</t>
+          <t>https://m.place.naver.com/place/1189916238</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,34 +1250,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>팀윤짐 PT 송도7호점</t>
+          <t>더피티짐 프리미엄 더테라스점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>teamyoon_7@naver.com</t>
+          <t>gktk1877@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1487-9688</t>
+          <t>0507-1307-1061</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 161 더하이츠 5층 507호</t>
+          <t>인천 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamyoon_7</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1263,15 +1287,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5icxb</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>567</v>
+        <v>47</v>
       </c>
       <c r="Q9" t="n">
-        <v>1301</v>
+        <v>449</v>
       </c>
       <c r="R9" t="n">
-        <v>1868</v>
+        <v>496</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1876943780</t>
+          <t>1296216271</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1876943780</t>
+          <t>https://m.place.naver.com/place/1296216271</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,39 +1348,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코어앤모어 PT</t>
+          <t>FWC스포츠센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>coreandmore@naver.com</t>
+          <t>fwcsports@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1319-5328</t>
+          <t>0507-1360-7005</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
+          <t>http://www.fwcsongdo.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1362,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qg2m</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="Q10" t="n">
-        <v>109</v>
+        <v>643</v>
       </c>
       <c r="R10" t="n">
-        <v>188</v>
+        <v>851</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,15 +1424,113 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2021439008</t>
+          <t>34249321</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021439008</t>
+          <t>https://m.place.naver.com/place/34249321</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>팀윤짐 PT 송도7호점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>teamyoon_7@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1487-9688</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>인천 연수구 신송로 161 더하이츠 5층 507호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teamyoon_7</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4l4no</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>567</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1301</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1868</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1876943780</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1876943780</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>여성전용PT 핏투핏 송도점</t>
+          <t>메이드핏바이브래이디</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>waterfallbody@naver.com</t>
+          <t>redgoldmy@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1458-9510</t>
+          <t>0507-1470-3049</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 연수구 아트센터대로 87 401동 2층 210호</t>
+          <t>인천광역시 연수구 송도미래로11번길 27 A동 310호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/waterfallbody</t>
+          <t>https://www.instagram.com/madefit_by_brady</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdg5hky</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>137</v>
+        <v>14</v>
       </c>
       <c r="Q2" t="n">
-        <v>780</v>
+        <v>9</v>
       </c>
       <c r="R2" t="n">
-        <v>917</v>
+        <v>23</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1851119903</t>
+          <t>1176352806</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1851119903</t>
+          <t>https://m.place.naver.com/place/1176352806</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>룩바디짐 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>lukbody@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1462-2244</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천광역시 연수구 하모니로138번길 11 101동 401호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness/</t>
+          <t>https://blog.naver.com/lukbody</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +695,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1358</v>
+        <v>305</v>
       </c>
       <c r="Q3" t="n">
-        <v>920</v>
+        <v>338</v>
       </c>
       <c r="R3" t="n">
-        <v>2278</v>
+        <v>643</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1909769673</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1909769673</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,39 +752,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>센트럴피티스튜디오 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>centralptstudio@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1417-2729</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천광역시 연수구 센트럴로 232 센1몰 A동 208호~210호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -807,7 +799,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mk22</t>
+          <t>https://talk.naver.com/ct/w45ang</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>315</v>
+        <v>152</v>
       </c>
       <c r="Q4" t="n">
-        <v>1816</v>
+        <v>673</v>
       </c>
       <c r="R4" t="n">
-        <v>2131</v>
+        <v>825</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>1627643135</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/1627643135</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>프롬바디PT&amp;필라테스 인천대입구역점</t>
+          <t>헤라클레스짐 PT&amp;헬스 송도점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>from-body@naver.com</t>
+          <t>mee_hwa90@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1425-0923</t>
+          <t>0507-1325-2728</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 연수구 하모니로138번길 11 송도캐슬센트럴파크 102동 324호</t>
+          <t>인천광역시 연수구 하모니로178번길 22 GTX센트럴상가 B동 9층 헤라클레스짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://frombody.kr</t>
+          <t>http://헤라클레스짐송도점.kr/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,27 +882,23 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ofx5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="Q5" t="n">
-        <v>1543</v>
+        <v>732</v>
       </c>
       <c r="R5" t="n">
-        <v>1834</v>
+        <v>1016</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1472986584</t>
+          <t>1276642503</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472986584</t>
+          <t>https://m.place.naver.com/place/1276642503</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 송도점</t>
+          <t>라프그라운드PT 송도점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>physiostudio_7@naver.com</t>
+          <t>lfitness2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1356-5739</t>
+          <t>0507-1461-8028</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
+          <t>인천광역시 연수구 해돋이로 168-2 601호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/physiostudio_7</t>
+          <t>http://lafground.com/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -998,17 +986,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wual9v3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="Q6" t="n">
-        <v>449</v>
+        <v>64</v>
       </c>
       <c r="R6" t="n">
-        <v>506</v>
+        <v>97</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2019067639</t>
+          <t>1488275180</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019067639</t>
+          <t>https://m.place.naver.com/place/1488275180</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,56 +1038,48 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>매드볼릭 PT 헬스장 송도</t>
+          <t>송도 진영쌤</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>madbolic-songdo@naver.com</t>
+          <t>eight-pt@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1352-6741</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+          <t>인천광역시 연수구 송도과학로27번길 55</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/madbolic-songdo</t>
+          <t>http://coconutz.kr/14253</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46104</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>559</v>
+        <v>71</v>
       </c>
       <c r="Q7" t="n">
-        <v>1242</v>
+        <v>82</v>
       </c>
       <c r="R7" t="n">
-        <v>1801</v>
+        <v>153</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,61 +1106,61 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1206099126</t>
+          <t>1308646857</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206099126</t>
+          <t>https://m.place.naver.com/place/1308646857</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더피티짐 헬스&amp;PT 글로벌캠퍼스점</t>
+          <t>짐작 PT &amp; 헬스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kyu0000000@naver.com</t>
+          <t>gymzak@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1320-3080</t>
+          <t>0507-1469-0425</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 연수구 송도문화로28번길 28 글로벌캠퍼스푸르지오상가 202동 2층 208-210호</t>
+          <t>인천광역시 연수구 해돋이로152번길 9 1동 3층 305호,306호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://thepit.creatorlink.net</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1199,12 +1175,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dk13</t>
+          <t>https://talk.naver.com/ct/w4s5s4</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>334</v>
+        <v>187</v>
       </c>
       <c r="Q8" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="R8" t="n">
-        <v>1034</v>
+        <v>587</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1189916238</t>
+          <t>1392612926</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189916238</t>
+          <t>https://m.place.naver.com/place/1392612926</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 더테라스점</t>
+          <t>피플운동센터 재활&amp;PT 송도타임스페이스점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gktk1877@naver.com</t>
+          <t>physioplace-@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1307-1061</t>
+          <t>0507-1491-0647</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
+          <t>인천광역시 연수구 하모니로 158 송도 타임스페이스 B동 904호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>http://www.physioplace.co.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,12 +1273,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5icxb</t>
+          <t>https://talk.naver.com/ct/w7agvt5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>449</v>
+        <v>300</v>
       </c>
       <c r="R9" t="n">
-        <v>496</v>
+        <v>349</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1302,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1296216271</t>
+          <t>1097730397</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296216271</t>
+          <t>https://m.place.naver.com/place/1097730397</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1348,34 +1324,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FWC스포츠센터</t>
+          <t>피티시모 인천송도점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fwcsports@naver.com</t>
+          <t>qkrrudrnjs49@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1360-7005</t>
+          <t>0507-1307-8879</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
+          <t>인천광역시 연수구 송도국제대로 165 홈플러스복합쇼핑몰 2층 X7호, YH호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.fwcsongdo.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1395,7 +1371,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4qg2m</t>
+          <t>https://talk.naver.com/ct/w49t8x</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>208</v>
+        <v>144</v>
       </c>
       <c r="Q10" t="n">
-        <v>643</v>
+        <v>185</v>
       </c>
       <c r="R10" t="n">
-        <v>851</v>
+        <v>329</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1400,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>34249321</t>
+          <t>1527801882</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34249321</t>
+          <t>https://m.place.naver.com/place/1527801882</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1446,29 +1422,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>팀윤짐 PT 송도7호점</t>
+          <t>리버스바디 센트럴점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>teamyoon_7@naver.com</t>
+          <t>reverse-gym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1487-9688</t>
+          <t>0507-1461-6781</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 연수구 신송로 161 더하이츠 5층 507호</t>
+          <t>인천광역시 연수구 해돋이로 160-19 5층 506호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamyoon_7</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,12 +1454,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,46 +1469,6336 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>https://talk.naver.com/ct/w463st</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>81</v>
+      </c>
+      <c r="R11" t="n">
+        <v>114</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1149265237</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1149265237</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>영어교육</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ISL잉글리쉬피티학원</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>em_13@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1497-6102</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 168-7 레드원 프라자 3층 301호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>44</v>
+      </c>
+      <c r="R12" t="n">
+        <v>44</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2022597831</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2022597831</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>포에버핏퍼스널트레이닝 인천송도7호점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4everfit7@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>032-834-9778</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 122 송도프라자</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>http://www.4everfit.co.kr/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>17</v>
+      </c>
+      <c r="R13" t="n">
+        <v>24</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>34666226</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34666226</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>준토스핏PT 송도 트리플점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>juntosfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1304-4383</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로28번길 8 207호 준토스핏</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gk1n</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1584</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1740</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1859724879</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1859724879</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>샤머니짐 송도점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>resort_6@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1330-9030</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1382</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>931</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2313</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1040543457</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1040543457</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>짐투투 헬스&amp;PT 송도점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>gym22-@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1368-4473</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로 69 3층 309호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wq1wv1m</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>613</v>
+      </c>
+      <c r="R16" t="n">
+        <v>716</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1692085107</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1692085107</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>무포스 PT FT 송도점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>moveforstrength@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1406-4500</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.moveforstrength.co.kr/</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5x24z</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>644</v>
+      </c>
+      <c r="R17" t="n">
+        <v>758</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1426191152</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1426191152</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>더피티짐 프리미엄 더테라스점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>qoqofh677@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1307-1061</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://theptgym.clickn.co.kr/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5icxb</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>648</v>
+      </c>
+      <c r="R18" t="n">
+        <v>694</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1296216271</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1296216271</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>송도 리엠PT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>fldpavlxl22@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1306-9102</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 168-7 레드원프라자 6층 603호 리엠PT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w48nfm</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>497</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>894</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1391</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1533793344</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1533793344</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>아인스멀티짐 송도점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>einsmultigym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1405-4501</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 166 플러스원 프라자 5층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4wz5f</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1444</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1646</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>35352221</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35352221</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MM pt</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dleodnjs13@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1417-9696</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로 131 202동 2층 221호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4xi6p</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>221</v>
+      </c>
+      <c r="R21" t="n">
+        <v>341</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>37942571</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37942571</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>환스튜디오PT 송도점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hwansstudio@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1436-1273</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로16번길 13-39 1층 환스튜디오</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qk5e</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>268</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>898</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1166</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1260247315</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1260247315</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>더피티짐 프리미엄 학원가점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>qoqofh677@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1446-9681</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://theptgym.clickn.co.kr/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mk22</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1921</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2238</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1063156519</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1063156519</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>임팩트 짐, 헬스 / PT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>znzl6268@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1383-9474</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로168번길 101 랜드마크푸르지오시티 3층 임팩트 짐</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>57</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1118917592</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1118917592</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>치프 스포츠 트레이닝 재활PT센터</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>jayayy88@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1475-0952</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크 101동 507호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wywmht2</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>37</v>
+      </c>
+      <c r="R25" t="n">
+        <v>45</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1668102513</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1668102513</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>매크로짐</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>macrogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1333-2578</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 15 상가 지하 1층, B116호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>10</v>
+      </c>
+      <c r="R26" t="n">
+        <v>22</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2083828411</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2083828411</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>에이바디스튜디오 PT 송도점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>abodystudio@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>032-858-0119</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로 131 202동 2층 221호 에이바디스튜디오 송도점</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://abodypt.com/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>144</v>
+      </c>
+      <c r="R27" t="n">
+        <v>264</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1188832610</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1188832610</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>하이어짐PT 송도점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>highsongdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1474-8260</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 110 은진프라자 2층 하이어짐PT 송도점</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a4xp</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1234</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1403</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1642474825</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1642474825</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>피지컬랩 송도PT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>maxyh7@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1332-2194</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 테크노파크로111번길 11 시카고 타워 502호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4umh7</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>544</v>
+      </c>
+      <c r="R29" t="n">
+        <v>730</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1826127652</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1826127652</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>히든핏 PT&amp;헬스 송도점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>hiddenfit__@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1349-9712</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로28번길 50 더샵 송도트리플타워west동 2층 219~221호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7i3g95</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>560</v>
+      </c>
+      <c r="R30" t="n">
+        <v>740</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1355031564</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1355031564</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>송도PT 준토스핏 프리미엄점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>juntosfitpremium@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1443-1973</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로130번길 20 6층 602~4호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.juntosfitpremium.com</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wm7cqeu</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>251</v>
+      </c>
+      <c r="R31" t="n">
+        <v>295</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2020902408</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2020902408</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>클래식더짐 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>happy3747@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1368-4594</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로125번길 7 이리옴프라자 5층 505호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5sj</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>526</v>
+      </c>
+      <c r="R32" t="n">
+        <v>605</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1148859143</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1148859143</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>뉴젠 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>new-gen@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1375-1998</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로180번길 11 상가 A동 3층 315호</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hw0l</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>406</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1624</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2030</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1587802368</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1587802368</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>아리스 휘트니스 퓨어</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>aris_songdo_pure@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1388-9683</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 160-14 8, 9층 전체</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wqwdvgu</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>116</v>
+      </c>
+      <c r="R34" t="n">
+        <v>269</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2033238108</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2033238108</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>매드볼릭 PT 헬스장 송도</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>madbolic-songdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1352-6741</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/madbolic-songdo</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>574</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1306</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1880</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1206099126</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1206099126</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>퍼스트짐 PT&amp;헬스 송도점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>tynsongdo12@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1497-9061</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 컨벤시아대로230번길 54 닥터플러스몰 3층 311~314호 퍼스트짐 송도점</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w487dq</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>506</v>
+      </c>
+      <c r="R36" t="n">
+        <v>694</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1140180251</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1140180251</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>피트니스진심</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>fitness_jinsim@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1370-1215</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해송로30번길 34-18 2층 피트니스진심</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w458tu</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>307</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>980</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1287</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1251981221</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1251981221</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>마제스티짐 2호</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>majestygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 랜드마크로 68 301동 201~203호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/majestygym_official?igsh=MTJ2NGQ0d2c3eWVlMQ==</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>115</v>
+      </c>
+      <c r="R38" t="n">
+        <v>138</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1012283256</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1012283256</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>리버스바디</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>reverse-gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1414-6778</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 55 3층 302, 303호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/reverse-gym</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>379</v>
+      </c>
+      <c r="R39" t="n">
+        <v>564</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>37928664</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37928664</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ok바디짐</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>okbodygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1429-0678</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로54번길 15-5 201호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>68</v>
+      </c>
+      <c r="R40" t="n">
+        <v>77</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>399153012</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/399153012</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>투빅짐 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ghqkr3904@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1469-7866</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로 87 커낼워크 겨울동 402동 투빅짐</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfdus</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>81</v>
+      </c>
+      <c r="R41" t="n">
+        <v>157</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1223908783</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1223908783</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>여성전용PT 핏투핏 송도점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>waterfallbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1458-9510</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로 87 401동 2층 210호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdg5hky</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>815</v>
+      </c>
+      <c r="R42" t="n">
+        <v>952</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1851119903</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1851119903</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>핏더라운지 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>fitthelounge_@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1339-9679</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로168번길 100 G동 2층 248-250호 핏더라운지</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r791</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1173</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1536</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1726182684</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1726182684</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>솔루션피트니스</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>solution_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1392-2038</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 송도씨워크인테라스한라 c동 346~354</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4llam</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>459</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>319</v>
+      </c>
+      <c r="R44" t="n">
+        <v>778</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1392113756</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1392113756</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>풀바디짐 헬스&amp;PT 송도점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>byun0124@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1395-0448</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 6층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4zxk4</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>420</v>
+      </c>
+      <c r="R45" t="n">
+        <v>630</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1302214665</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1302214665</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>고다짐 송도점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>godagym_sd@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1391-5466</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 114 지층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.godagym.com</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vjro</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>272</v>
+      </c>
+      <c r="R46" t="n">
+        <v>385</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1692050159</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1692050159</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>피트니스 연구소 송도점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>lfitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1468-2286</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>http://fitnessinstitute.co.kr/</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pxzz</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1567</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>731</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2298</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1806077033</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1806077033</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>국가대표PT 빅토리짐 1공구점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>vtrgym_songdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1329-9017</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 160-6 3층 303호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41bqd</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>276</v>
+      </c>
+      <c r="R48" t="n">
+        <v>420</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1501800955</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1501800955</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>라이크짐 송도</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>kybayo112@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1346-9492</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 첨단대로 80 레지던스 라이크홈 2층 208호 라이크짐</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vtwb</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>23</v>
+      </c>
+      <c r="R49" t="n">
+        <v>106</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1379614052</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1379614052</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>최박사헬스케어</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>chlansrl58@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1320-0171</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 A동 407호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>9</v>
+      </c>
+      <c r="R50" t="n">
+        <v>69</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1939728456</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1939728456</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>더피티짐 헬스&amp;PT 글로벌캠퍼스점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>heeyoun9304@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1320-3080</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도문화로28번길 28 글로벌캠퍼스푸르지오상가 202동 2층 208-210호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://thepit.creatorlink.net</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dk13</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>332</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>705</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1037</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1189916238</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1189916238</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>송도pt 프리코어 운동센터</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>pre_core@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1328-4238</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 상가 3층 312호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xwmi</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>109</v>
+      </c>
+      <c r="R52" t="n">
+        <v>203</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1572765040</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1572765040</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>모베레 메디컬트레이닝 전문센터</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>inhapac@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1343-3540</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 165 703호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>http://moverefitness.p-e.kr/</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcbaxw</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>485</v>
+      </c>
+      <c r="R53" t="n">
+        <v>576</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>38547816</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38547816</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>코어앤모어 PT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>coreandmore@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1319-5328</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmzjpfy</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>111</v>
+      </c>
+      <c r="R54" t="n">
+        <v>191</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2021439008</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2021439008</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>아늑 필라테스&amp;PT 송도국제업무지구역점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>88pilatespt@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1451-2412</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로 323 상가동 3층 디309호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w8ga10y</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>251</v>
+      </c>
+      <c r="R55" t="n">
+        <v>315</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1522243678</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1522243678</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>3HOPT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>sam926@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1392-8317</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로120번길 23 아크리아2 2층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wmm1</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>197</v>
+      </c>
+      <c r="R56" t="n">
+        <v>281</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1964708669</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1964708669</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>메트힐링짐</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>redgoldmy@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1430-1760</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 313 B동 335호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>9</v>
+      </c>
+      <c r="R57" t="n">
+        <v>11</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2035298615</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2035298615</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>헨리스짐</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>redgoldmy@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로27번길 55 캠퍼스타운 상가 B동 2층 215호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>6</v>
+      </c>
+      <c r="R58" t="n">
+        <v>17</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1584713546</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1584713546</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>제이스타짐 헬스장&amp;PT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>songdofitness_jstar@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1309-9696</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도미래로11번길 27 A동 4층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4l1v9</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>953</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1178</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1582467326</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1582467326</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>팀윤짐 PT 송도4호점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>teamyoonsongdo3@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1315-9683</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 센트럴로 160 A동 2층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://teamyoongym.com/440</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcedx2</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>425</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1099</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1524</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1338590785</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1338590785</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>헬스PT 런앤짐 여성전용 송도점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>runandgym_songdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1498-8928</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 112 4층 401, 402호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/runandgym_songdo/223794389191</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>205</v>
+      </c>
+      <c r="R61" t="n">
+        <v>388</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1881117008</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1881117008</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>스타크짐 PT 송도본점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>starkgym_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1433-7781</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로132번길 30 휴먼빌파크 6층 스타크짐 퍼스널 트레이닝 센터</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5x3ge</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>567</v>
+      </c>
+      <c r="R62" t="n">
+        <v>710</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1487669358</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1487669358</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>송도PT 볼드짐</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>bodyprincess@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1388-8284</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 D동 304, 305호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yqdb</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>43</v>
+      </c>
+      <c r="R63" t="n">
+        <v>120</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1509661314</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1509661314</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>송도PT 베럴핏</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sncbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1417-8999</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 114 서운프라자 3층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcajql</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>75</v>
+      </c>
+      <c r="R64" t="n">
+        <v>232</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>21732769</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21732769</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>티케이바디핏</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>tkbodyfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1476-0927</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 아트센터대로168번길 100 한라웨스턴파크송도 F동 240, 241호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>439</v>
+      </c>
+      <c r="R65" t="n">
+        <v>439</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1590712263</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1590712263</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>국대PT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>kookdaeteam_@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1397-1398</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로178번길 22 4층 413호(C동)</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>5</v>
+      </c>
+      <c r="R66" t="n">
+        <v>17</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1706457439</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1706457439</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>프롬바디PT&amp;필라테스 인천대입구역점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>yoonse1995@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1425-0923</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크 102동 324호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://frombody.kr</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ofx5</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>291</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1580</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1871</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1472986584</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1472986584</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>팀비스트짐 PT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>team_beast@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1368-8303</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 102 4층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gsem</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>1008</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>594</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1602</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1349969899</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1349969899</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>피지오스튜디오 필라테스 &amp; PT 송도점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>physiostudio2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1356-5739</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wual9v3</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>524</v>
+      </c>
+      <c r="R69" t="n">
+        <v>577</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>2019067639</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2019067639</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>더피티짐 헬스&amp;PT 리치센트럴점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>theptgym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1465-9304</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 인천타워대로197번길 16 리치센트럴 8층 810~811호 더피티짐</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://thepit.creatorlink.net</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a7jb</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1401</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1750</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1362792414</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1362792414</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>송도 피크짐 연중무휴 PT 헬스장</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>songdo_pikgym365@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1426-1817</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 연구단지로55번길 16 2층 229호 230호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/whm8lyp</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>147</v>
+      </c>
+      <c r="R71" t="n">
+        <v>272</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1110236566</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1110236566</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>리젠핏 스튜디오 PT 송도점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>regenfitstudio@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1437-1950</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로152번길 35 퍼스트프라자 604호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vwcy</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>664</v>
+      </c>
+      <c r="R72" t="n">
+        <v>821</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1874099957</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1874099957</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>트리플에이치스포츠그룹</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>fwcsongdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1382-7024</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 107 G동 3층 129호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>64</v>
+      </c>
+      <c r="R73" t="n">
+        <v>64</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1288221464</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1288221464</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>에스에이치 IT휘트니스점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>shsongdo84@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1434-8501</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 송도과학로 32 송도테크노파크IT센터 3층 IT휘트니스</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cpb5</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>718</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1149</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1867</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1206107606</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1206107606</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>로얄바디짐 PT 송도본점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>wnsvydkdl900@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 하모니로138번길 11 101동 210호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>http://royalbodygym.co.kr/</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>239</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>204</v>
+      </c>
+      <c r="R75" t="n">
+        <v>443</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1537732248</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1537732248</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>팀윤짐 PT 송도7호점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>teamyoon_7@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1487-9688</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 신송로 161 더하이츠 5층 507호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
           <t>https://talk.naver.com/ct/w4l4no</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
         <v>567</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1301</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1868</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="Q76" t="n">
+        <v>1308</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1875</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
         <is>
           <t>1876943780</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1876943780</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
+          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>15</v>
+        <v>1386</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>933</v>
       </c>
       <c r="R2" t="n">
-        <v>34</v>
+        <v>2319</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2074412271</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>키필라테스 청라점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>keypilates@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>1555-7745</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
+          <t>https://talk.naver.com/ct/wyozl7z</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1386</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
-        <v>933</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>2319</v>
+        <v>34</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>2074412271</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -824,10 +824,10 @@
         <v>317</v>
       </c>
       <c r="Q4" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="R4" t="n">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>53</v>
       </c>
       <c r="Q6" t="n">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="R6" t="n">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         <v>576</v>
       </c>
       <c r="Q7" t="n">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="R7" t="n">
-        <v>1889</v>
+        <v>1893</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1147,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>라프그라운드PT 송도점</t>
+          <t>무포스 PT FT 송도점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mingukang64@naver.com</t>
+          <t>moveforstrength@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1461-8028</t>
+          <t>0507-1406-4500</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 168-2 601호</t>
+          <t>인천 연수구 인천타워대로197번길 16 2층 226호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://lafground.com/</t>
+          <t>https://www.moveforstrength.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1194,13 +1194,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5x24z</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>644</v>
       </c>
       <c r="R8" t="n">
-        <v>97</v>
+        <v>759</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1488275180</t>
+          <t>1426191152</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488275180</t>
+          <t>https://m.place.naver.com/place/1426191152</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,44 +1250,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>팀윤짐 PT 송도7호점</t>
+          <t>FWC스포츠센터</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>teamyoon_7@naver.com</t>
+          <t>fwcsports@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1487-9688</t>
+          <t>0507-1360-7005</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 연수구 신송로 161 더하이츠 5층 507호</t>
+          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamyoon_7</t>
+          <t>http://www.fwcsongdo.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4l4no</t>
+          <t>https://talk.naver.com/ct/w4qg2m</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>567</v>
+        <v>208</v>
       </c>
       <c r="Q9" t="n">
-        <v>1309</v>
+        <v>643</v>
       </c>
       <c r="R9" t="n">
-        <v>1876</v>
+        <v>851</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1876943780</t>
+          <t>34249321</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1876943780</t>
+          <t>https://m.place.naver.com/place/34249321</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,34 +1348,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코어앤모어 PT</t>
+          <t>스타크짐 PT 송도본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>coreandmore@naver.com</t>
+          <t>starkgym_official@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1319-5328</t>
+          <t>0507-1433-7781</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+          <t>인천 연수구 인천타워대로132번길 30 휴먼빌파크 6층 스타크짐 퍼스널 트레이닝 센터</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
+          <t>http://pf.kakao.com/_UevaG</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1391,12 +1395,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmzjpfy</t>
+          <t>https://talk.naver.com/ct/w5x3ge</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="Q10" t="n">
-        <v>111</v>
+        <v>567</v>
       </c>
       <c r="R10" t="n">
-        <v>191</v>
+        <v>712</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2021439008</t>
+          <t>1487669358</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021439008</t>
+          <t>https://m.place.naver.com/place/1487669358</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,34 +1446,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모베레 메디컬트레이닝 전문센터</t>
+          <t>팀윤짐 PT 송도7호점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>inhapac@naver.com</t>
+          <t>teamyoon_7@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1343-3540</t>
+          <t>0507-1487-9688</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 165 703호</t>
+          <t>인천 연수구 신송로 161 더하이츠 5층 507호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://moverefitness.p-e.kr/</t>
+          <t>https://blog.naver.com/teamyoon_7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1489,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcbaxw</t>
+          <t>https://talk.naver.com/ct/w4l4no</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>91</v>
+        <v>567</v>
       </c>
       <c r="Q11" t="n">
-        <v>485</v>
+        <v>1309</v>
       </c>
       <c r="R11" t="n">
-        <v>576</v>
+        <v>1876</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,15 +1522,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38547816</t>
+          <t>1876943780</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38547816</t>
+          <t>https://m.place.naver.com/place/1876943780</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>코어앤모어 PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>coreandmore@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1319-5328</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmzjpfy</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>111</v>
+      </c>
+      <c r="R12" t="n">
+        <v>191</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2021439008</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2021439008</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -777,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +798,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4mk22</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -824,10 +816,10 @@
         <v>317</v>
       </c>
       <c r="Q4" t="n">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="R4" t="n">
-        <v>2242</v>
+        <v>2245</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -875,7 +867,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +892,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pxzz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1572</v>
+        <v>1578</v>
       </c>
       <c r="Q5" t="n">
         <v>731</v>
       </c>
       <c r="R5" t="n">
-        <v>2303</v>
+        <v>2309</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -956,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 송도점</t>
+          <t>매드볼릭 PT 헬스장 송도</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>physiostudio_7@naver.com</t>
+          <t>madbolic-songdo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1356-5739</t>
+          <t>0507-1352-6741</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
+          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/physiostudio_7</t>
+          <t>https://blog.naver.com/madbolic-songdo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -998,14 +986,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wual9v3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>53</v>
+        <v>576</v>
       </c>
       <c r="Q6" t="n">
-        <v>540</v>
+        <v>1318</v>
       </c>
       <c r="R6" t="n">
-        <v>593</v>
+        <v>1894</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2019067639</t>
+          <t>1206099126</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019067639</t>
+          <t>https://m.place.naver.com/place/1206099126</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>매드볼릭 PT 헬스장 송도</t>
+          <t>하이어짐PT 송도점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>madbolic-songdo@naver.com</t>
+          <t>highsongdo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1352-6741</t>
+          <t>0507-1474-8260</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+          <t>인천광역시 연수구 해돋이로 110 은진프라자 2층 하이어짐PT 송도점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/madbolic-songdo</t>
+          <t>https://blog.naver.com/highsongdo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1096,14 +1080,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46104</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>576</v>
+        <v>170</v>
       </c>
       <c r="Q7" t="n">
-        <v>1317</v>
+        <v>1293</v>
       </c>
       <c r="R7" t="n">
-        <v>1893</v>
+        <v>1463</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1206099126</t>
+          <t>1642474825</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206099126</t>
+          <t>https://m.place.naver.com/place/1642474825</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1169,7 +1149,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 연수구 인천타워대로197번길 16 2층 226호</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5x24z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1348,34 +1324,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스타크짐 PT 송도본점</t>
+          <t>팀윤짐 PT 송도7호점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>starkgym_official@naver.com</t>
+          <t>teamyoon_7@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1433-7781</t>
+          <t>0507-1487-9688</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 연수구 인천타워대로132번길 30 휴먼빌파크 6층 스타크짐 퍼스널 트레이닝 센터</t>
+          <t>인천광역시 연수구 신송로 161 더하이츠 5층 507호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_UevaG</t>
+          <t>https://blog.naver.com/teamyoon_7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,22 +1361,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5x3ge</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>145</v>
+        <v>567</v>
       </c>
       <c r="Q10" t="n">
-        <v>567</v>
+        <v>1309</v>
       </c>
       <c r="R10" t="n">
-        <v>712</v>
+        <v>1876</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1487669358</t>
+          <t>1876943780</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487669358</t>
+          <t>https://m.place.naver.com/place/1876943780</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,29 +1418,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>팀윤짐 PT 송도7호점</t>
+          <t>코어앤모어 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>teamyoon_7@naver.com</t>
+          <t>coreandmore@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1487-9688</t>
+          <t>0507-1319-5328</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 연수구 신송로 161 더하이츠 5층 507호</t>
+          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamyoon_7</t>
+          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,19 +1455,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4l4no</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1507,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>567</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="n">
-        <v>1309</v>
+        <v>111</v>
       </c>
       <c r="R11" t="n">
-        <v>1876</v>
+        <v>191</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,113 +1490,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1876943780</t>
+          <t>2021439008</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1876943780</t>
+          <t>https://m.place.naver.com/place/2021439008</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>코어앤모어 PT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>coreandmore@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1319-5328</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>인천 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wmzjpfy</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>111</v>
-      </c>
-      <c r="R12" t="n">
-        <v>191</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2021439008</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2021439008</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>키필라테스 청라점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>keypilates@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>1555-7745</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyozl7z</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1386</v>
+        <v>15</v>
       </c>
       <c r="Q2" t="n">
-        <v>933</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>2319</v>
+        <v>34</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>2074412271</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>1387</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>933</v>
       </c>
       <c r="R3" t="n">
-        <v>34</v>
+        <v>2320</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2074412271</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -816,10 +816,10 @@
         <v>317</v>
       </c>
       <c r="Q4" t="n">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="R4" t="n">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1127,34 +1127,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>무포스 PT FT 송도점</t>
+          <t>FWC스포츠센터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>moveforstrength@naver.com</t>
+          <t>fwcsports@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1406-4500</t>
+          <t>0507-1360-7005</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
+          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.moveforstrength.co.kr/</t>
+          <t>http://www.fwcsongdo.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,15 +1169,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qg2m</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="Q8" t="n">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="R8" t="n">
-        <v>759</v>
+        <v>851</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1208,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1426191152</t>
+          <t>34249321</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426191152</t>
+          <t>https://m.place.naver.com/place/34249321</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,39 +1230,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FWC스포츠센터</t>
+          <t>코어앤모어 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fwcsports@naver.com</t>
+          <t>coreandmore@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1360-7005</t>
+          <t>0507-1319-5328</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
+          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.fwcsongdo.com/</t>
+          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1268,14 +1272,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qg2m</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="Q9" t="n">
-        <v>643</v>
+        <v>111</v>
       </c>
       <c r="R9" t="n">
-        <v>851</v>
+        <v>191</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>34249321</t>
+          <t>2021439008</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34249321</t>
+          <t>https://m.place.naver.com/place/2021439008</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1324,34 +1324,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>팀윤짐 PT 송도7호점</t>
+          <t>모베레 메디컬트레이닝 전문센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>teamyoon_7@naver.com</t>
+          <t>inhapac@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1487-9688</t>
+          <t>0507-1343-3540</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 161 더하이츠 5층 507호</t>
+          <t>인천 연수구 해돋이로 165 703호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamyoon_7</t>
+          <t>http://moverefitness.p-e.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1366,10 +1366,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcbaxw</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1381,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>567</v>
+        <v>91</v>
       </c>
       <c r="Q10" t="n">
-        <v>1309</v>
+        <v>485</v>
       </c>
       <c r="R10" t="n">
-        <v>1876</v>
+        <v>576</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1400,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1876943780</t>
+          <t>38547816</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1876943780</t>
+          <t>https://m.place.naver.com/place/38547816</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1418,29 +1422,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>코어앤모어 PT</t>
+          <t>리버스바디</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>coreandmore@naver.com</t>
+          <t>reverse-gym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1319-5328</t>
+          <t>0507-1414-6778</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+          <t>인천광역시 연수구 송도과학로27번길 55 3층 302, 303호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
+          <t>https://blog.naver.com/reverse-gym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1455,7 +1459,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1475,13 +1479,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="Q11" t="n">
-        <v>111</v>
+        <v>382</v>
       </c>
       <c r="R11" t="n">
-        <v>191</v>
+        <v>573</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,12 +1494,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2021439008</t>
+          <t>37928664</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021439008</t>
+          <t>https://m.place.naver.com/place/37928664</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>resort_6@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
+          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>15</v>
+        <v>1387</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>933</v>
       </c>
       <c r="R2" t="n">
-        <v>34</v>
+        <v>2320</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2074412271</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>키필라테스 청라점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>keypilates@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>1555-7745</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyozl7z</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1387</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
-        <v>933</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>2320</v>
+        <v>34</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>2074412271</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -773,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mk22</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -838,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -867,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+          <t>인천 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -892,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pxzz</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -932,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -961,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+          <t>인천 연수구 테크노파크로111번길 11 시카고타워 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46104</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1004,10 +1020,10 @@
         <v>576</v>
       </c>
       <c r="Q6" t="n">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="R6" t="n">
-        <v>1894</v>
+        <v>1899</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1026,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 110 은진프라자 2층 하이어짐PT 송도점</t>
+          <t>인천 연수구 해돋이로 110 은진프라자 2층 하이어짐PT 송도점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1080,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a4xp</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1098,10 +1118,10 @@
         <v>170</v>
       </c>
       <c r="Q7" t="n">
-        <v>1293</v>
+        <v>1306</v>
       </c>
       <c r="R7" t="n">
-        <v>1463</v>
+        <v>1476</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1120,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1230,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코어앤모어 PT</t>
+          <t>팀윤짐 PT 송도7호점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>coreandmore@naver.com</t>
+          <t>teamyoon_7@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1319-5328</t>
+          <t>0507-1487-9688</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+          <t>인천 연수구 신송로 161 더하이츠 5층 507호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
+          <t>https://blog.naver.com/teamyoon_7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1267,15 +1287,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4l4no</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1287,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>80</v>
+        <v>567</v>
       </c>
       <c r="Q9" t="n">
-        <v>111</v>
+        <v>1309</v>
       </c>
       <c r="R9" t="n">
-        <v>191</v>
+        <v>1876</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2021439008</t>
+          <t>1876943780</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021439008</t>
+          <t>https://m.place.naver.com/place/1876943780</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1324,34 +1348,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모베레 메디컬트레이닝 전문센터</t>
+          <t>코어앤모어 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>inhapac@naver.com</t>
+          <t>coreandmore@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1343-3540</t>
+          <t>0507-1319-5328</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 165 703호</t>
+          <t>인천 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://moverefitness.p-e.kr/</t>
+          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1361,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1371,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcbaxw</t>
+          <t>https://talk.naver.com/ct/wmzjpfy</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1385,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="n">
-        <v>485</v>
+        <v>111</v>
       </c>
       <c r="R10" t="n">
-        <v>576</v>
+        <v>191</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38547816</t>
+          <t>2021439008</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38547816</t>
+          <t>https://m.place.naver.com/place/2021439008</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1422,34 +1446,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>리버스바디</t>
+          <t>모베레 메디컬트레이닝 전문센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>reverse-gym@naver.com</t>
+          <t>inhapac@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1414-6778</t>
+          <t>0507-1343-3540</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로27번길 55 3층 302, 303호</t>
+          <t>인천 연수구 해돋이로 165 703호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/reverse-gym</t>
+          <t>http://moverefitness.p-e.kr/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1464,10 +1488,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcbaxw</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1479,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="Q11" t="n">
-        <v>382</v>
+        <v>485</v>
       </c>
       <c r="R11" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1494,17 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>37928664</t>
+          <t>38547816</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37928664</t>
+          <t>https://m.place.naver.com/place/38547816</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>여성전용PT 핏투핏 송도점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>resort_6@naver.com</t>
+          <t>waterfallbody@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1458-9510</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천광역시 연수구 아트센터대로 87 401동 2층 210호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/waterfallbody</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,24 +596,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1387</v>
+        <v>137</v>
       </c>
       <c r="Q2" t="n">
-        <v>933</v>
+        <v>825</v>
       </c>
       <c r="R2" t="n">
-        <v>2320</v>
+        <v>962</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1851119903</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1851119903</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>1387</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>933</v>
       </c>
       <c r="R3" t="n">
-        <v>34</v>
+        <v>2320</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2074412271</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,39 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>키필라테스 청라점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>keypilates@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>1555-7745</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,7 +799,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mk22</t>
+          <t>https://talk.naver.com/ct/wyozl7z</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>317</v>
+        <v>15</v>
       </c>
       <c r="Q4" t="n">
-        <v>1930</v>
+        <v>19</v>
       </c>
       <c r="R4" t="n">
-        <v>2247</v>
+        <v>34</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>2074412271</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피트니스 연구소 송도점 헬스PT</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fitnessinssongdo@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1468-2286</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,22 +887,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pxzz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1578</v>
+        <v>317</v>
       </c>
       <c r="Q5" t="n">
-        <v>731</v>
+        <v>1933</v>
       </c>
       <c r="R5" t="n">
-        <v>2309</v>
+        <v>2250</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1806077033</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806077033</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>매드볼릭 PT 헬스장 송도</t>
+          <t>피트니스 연구소 송도점 헬스PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>madbolic-songdo@naver.com</t>
+          <t>fitnessinssongdo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1352-6741</t>
+          <t>0507-1468-2286</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/madbolic-songdo</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -998,17 +986,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46104</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>576</v>
+        <v>1578</v>
       </c>
       <c r="Q6" t="n">
-        <v>1323</v>
+        <v>731</v>
       </c>
       <c r="R6" t="n">
-        <v>1899</v>
+        <v>2309</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1206099126</t>
+          <t>1806077033</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206099126</t>
+          <t>https://m.place.naver.com/place/1806077033</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>하이어짐PT 송도점</t>
+          <t>매드볼릭 PT 헬스장 송도</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>highsongdo@naver.com</t>
+          <t>madbolic-songdo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1474-8260</t>
+          <t>0507-1352-6741</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 110 은진프라자 2층 하이어짐PT 송도점</t>
+          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/highsongdo</t>
+          <t>https://blog.naver.com/madbolic-songdo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1096,14 +1080,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4a4xp</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>170</v>
+        <v>576</v>
       </c>
       <c r="Q7" t="n">
-        <v>1306</v>
+        <v>1326</v>
       </c>
       <c r="R7" t="n">
-        <v>1476</v>
+        <v>1902</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1642474825</t>
+          <t>1206099126</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1642474825</t>
+          <t>https://m.place.naver.com/place/1206099126</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,56 +1132,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FWC스포츠센터</t>
+          <t>하이어짐PT 송도점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fwcsports@naver.com</t>
+          <t>highsongdo@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1360-7005</t>
+          <t>0507-1474-8260</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
+          <t>인천광역시 연수구 해돋이로 110 은진프라자 2층 하이어짐PT 송도점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.fwcsongdo.com/</t>
+          <t>https://blog.naver.com/highsongdo</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qg2m</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="Q8" t="n">
-        <v>643</v>
+        <v>1316</v>
       </c>
       <c r="R8" t="n">
-        <v>851</v>
+        <v>1486</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>34249321</t>
+          <t>1642474825</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34249321</t>
+          <t>https://m.place.naver.com/place/1642474825</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,34 +1226,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>팀윤짐 PT 송도7호점</t>
+          <t>더피티짐 프리미엄 더테라스점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>teamyoon_7@naver.com</t>
+          <t>gktk1877@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1487-9688</t>
+          <t>0507-1307-1061</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 연수구 신송로 161 더하이츠 5층 507호</t>
+          <t>인천광역시 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamyoon_7</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1287,19 +1263,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4l4no</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>567</v>
+        <v>46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1309</v>
+        <v>663</v>
       </c>
       <c r="R9" t="n">
-        <v>1876</v>
+        <v>709</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1876943780</t>
+          <t>1296216271</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1876943780</t>
+          <t>https://m.place.naver.com/place/1296216271</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,39 +1320,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코어앤모어 PT</t>
+          <t>FWC스포츠센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>coreandmore@naver.com</t>
+          <t>fwcsports@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1319-5328</t>
+          <t>0507-1360-7005</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
+          <t>http://www.fwcsongdo.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1395,7 +1367,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmzjpfy</t>
+          <t>https://talk.naver.com/ct/w4qg2m</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="Q10" t="n">
-        <v>111</v>
+        <v>643</v>
       </c>
       <c r="R10" t="n">
-        <v>191</v>
+        <v>851</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2021439008</t>
+          <t>34249321</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021439008</t>
+          <t>https://m.place.naver.com/place/34249321</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,91 +1418,181 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모베레 메디컬트레이닝 전문센터</t>
+          <t>코어앤모어 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>inhapac@naver.com</t>
+          <t>coreandmore@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1343-3540</t>
+          <t>0507-1319-5328</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 165 703호</t>
+          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>111</v>
+      </c>
+      <c r="R11" t="n">
+        <v>191</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2021439008</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2021439008</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>모베레 메디컬트레이닝 전문센터</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>inhapac@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1343-3540</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 연수구 해돋이로 165 703호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>http://moverefitness.p-e.kr/</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcbaxw</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>91</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>485</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>576</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>38547816</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/38547816</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -624,10 +624,10 @@
         <v>137</v>
       </c>
       <c r="Q2" t="n">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="R2" t="n">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="Q3" t="n">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="R3" t="n">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -910,10 +910,10 @@
         <v>317</v>
       </c>
       <c r="Q5" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="R5" t="n">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="Q7" t="n">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="R7" t="n">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         <v>170</v>
       </c>
       <c r="Q8" t="n">
-        <v>1316</v>
+        <v>1323</v>
       </c>
       <c r="R8" t="n">
-        <v>1486</v>
+        <v>1493</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1226,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 더테라스점</t>
+          <t>라프그라운드PT 송도점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gktk1877@naver.com</t>
+          <t>mingukang64@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1307-1061</t>
+          <t>0507-1461-8028</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
+          <t>인천광역시 연수구 해돋이로 168-2 601호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>http://lafground.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1274,7 +1274,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="Q9" t="n">
-        <v>663</v>
+        <v>64</v>
       </c>
       <c r="R9" t="n">
-        <v>709</v>
+        <v>97</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1296216271</t>
+          <t>1488275180</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296216271</t>
+          <t>https://m.place.naver.com/place/1488275180</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FWC스포츠센터</t>
+          <t>더피티짐 프리미엄 더테라스점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fwcsports@naver.com</t>
+          <t>gktk1877@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1360-7005</t>
+          <t>0507-1307-1061</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
+          <t>인천광역시 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.fwcsongdo.com/</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1362,14 +1362,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qg2m</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1381,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>208</v>
+        <v>46</v>
       </c>
       <c r="Q10" t="n">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="R10" t="n">
-        <v>851</v>
+        <v>709</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>34249321</t>
+          <t>1296216271</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34249321</t>
+          <t>https://m.place.naver.com/place/1296216271</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1499,100 +1495,6 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>모베레 메디컬트레이닝 전문센터</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>inhapac@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1343-3540</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>인천광역시 연수구 해돋이로 165 703호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>http://moverefitness.p-e.kr/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>91</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>485</v>
-      </c>
-      <c r="R12" t="n">
-        <v>576</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>38547816</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/38547816</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>여성전용PT 핏투핏 송도점</t>
+          <t>키필라테스 청라점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>waterfallbody@naver.com</t>
+          <t>keypilates@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1458-9510</t>
+          <t>1555-7745</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로 87 401동 2층 210호</t>
+          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/waterfallbody</t>
+          <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyozl7z</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="Q2" t="n">
-        <v>830</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>967</v>
+        <v>34</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1851119903</t>
+          <t>2074412271</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1851119903</t>
+          <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -663,7 +667,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>resort_6@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -680,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -718,10 +726,10 @@
         <v>1386</v>
       </c>
       <c r="Q3" t="n">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="R3" t="n">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,46 +748,46 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -799,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
+          <t>https://talk.naver.com/ct/w4mk22</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="Q4" t="n">
-        <v>19</v>
+        <v>1935</v>
       </c>
       <c r="R4" t="n">
-        <v>34</v>
+        <v>2252</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2074412271</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -850,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>피트니스 연구소 송도점 헬스PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>lfitness2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1468-2286</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,18 +895,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pxzz</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>317</v>
+        <v>1579</v>
       </c>
       <c r="Q5" t="n">
-        <v>1934</v>
+        <v>731</v>
       </c>
       <c r="R5" t="n">
-        <v>2251</v>
+        <v>2310</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>1806077033</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/1806077033</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -944,55 +956,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피트니스 연구소 송도점 헬스PT</t>
+          <t>매드볼릭 PT 헬스장 송도</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fitnessinssongdo@naver.com</t>
+          <t>madbolic-songdo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1468-2286</t>
+          <t>0507-1352-6741</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46104</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1001,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1578</v>
+        <v>577</v>
       </c>
       <c r="Q6" t="n">
-        <v>731</v>
+        <v>1328</v>
       </c>
       <c r="R6" t="n">
-        <v>2309</v>
+        <v>1905</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1806077033</t>
+          <t>1206099126</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806077033</t>
+          <t>https://m.place.naver.com/place/1206099126</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>매드볼릭 PT 헬스장 송도</t>
+          <t>하이어짐PT 송도점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>madbolic-songdo@naver.com</t>
+          <t>highsongdo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1352-6741</t>
+          <t>0507-1474-8260</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+          <t>인천광역시 연수구 해돋이로 110 은진프라자 2층 하이어짐PT 송도점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/madbolic-songdo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,20 +1086,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a4xp</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>577</v>
+        <v>170</v>
       </c>
       <c r="Q7" t="n">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="R7" t="n">
-        <v>1904</v>
+        <v>1494</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1206099126</t>
+          <t>1642474825</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206099126</t>
+          <t>https://m.place.naver.com/place/1642474825</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1132,34 +1152,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>하이어짐PT 송도점</t>
+          <t>라프그라운드PT 송도점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>highsongdo@naver.com</t>
+          <t>lfitness2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1474-8260</t>
+          <t>0507-1461-8028</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 110 은진프라자 2층 하이어짐PT 송도점</t>
+          <t>인천광역시 연수구 해돋이로 168-2 601호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/highsongdo</t>
+          <t>http://lafground.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1180,7 +1200,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>170</v>
+        <v>33</v>
       </c>
       <c r="Q8" t="n">
-        <v>1323</v>
+        <v>64</v>
       </c>
       <c r="R8" t="n">
-        <v>1493</v>
+        <v>97</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1642474825</t>
+          <t>1488275180</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1642474825</t>
+          <t>https://m.place.naver.com/place/1488275180</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>라프그라운드PT 송도점</t>
+          <t>무포스 PT FT 송도점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mingukang64@naver.com</t>
+          <t>moveforstrength@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1461-8028</t>
+          <t>0507-1406-4500</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 601호</t>
+          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://lafground.com/</t>
+          <t>https://www.moveforstrength.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1258,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1268,13 +1288,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5x24z</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1283,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="Q9" t="n">
-        <v>64</v>
+        <v>645</v>
       </c>
       <c r="R9" t="n">
-        <v>97</v>
+        <v>760</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1488275180</t>
+          <t>1426191152</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488275180</t>
+          <t>https://m.place.naver.com/place/1426191152</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1320,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 더테라스점</t>
+          <t>FWC스포츠센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gktk1877@naver.com</t>
+          <t>fwcsports@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1307-1061</t>
+          <t>0507-1360-7005</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
+          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>http://www.fwcsongdo.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,7 +1376,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1362,10 +1386,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4qg2m</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>46</v>
+        <v>208</v>
       </c>
       <c r="Q10" t="n">
-        <v>663</v>
+        <v>643</v>
       </c>
       <c r="R10" t="n">
-        <v>709</v>
+        <v>851</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,111 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1296216271</t>
+          <t>34249321</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296216271</t>
+          <t>https://m.place.naver.com/place/34249321</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>코어앤모어 PT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>coreandmore@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1319-5328</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>111</v>
-      </c>
-      <c r="R11" t="n">
-        <v>191</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2021439008</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2021439008</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>resort_6@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>15</v>
+        <v>1386</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>938</v>
       </c>
       <c r="R2" t="n">
-        <v>34</v>
+        <v>2324</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2074412271</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,39 +662,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>resort_6@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1386</v>
+        <v>317</v>
       </c>
       <c r="Q3" t="n">
-        <v>936</v>
+        <v>1938</v>
       </c>
       <c r="R3" t="n">
-        <v>2322</v>
+        <v>2255</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>피트니스 연구소 송도점 헬스PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>lfitness2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1468-2286</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,12 +803,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mk22</t>
+          <t>https://talk.naver.com/ct/w4pxzz</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>317</v>
+        <v>1581</v>
       </c>
       <c r="Q4" t="n">
-        <v>1935</v>
+        <v>732</v>
       </c>
       <c r="R4" t="n">
-        <v>2252</v>
+        <v>2313</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>1806077033</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/1806077033</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,44 +854,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피트니스 연구소 송도점 헬스PT</t>
+          <t>매드볼릭 PT 헬스장 송도</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lfitness2@naver.com</t>
+          <t>madbolic-songdo@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1468-2286</t>
+          <t>0507-1352-6741</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,12 +901,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pxzz</t>
+          <t>https://talk.naver.com/ct/w46104</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1579</v>
+        <v>578</v>
       </c>
       <c r="Q5" t="n">
-        <v>731</v>
+        <v>1334</v>
       </c>
       <c r="R5" t="n">
-        <v>2310</v>
+        <v>1912</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1806077033</t>
+          <t>1206099126</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806077033</t>
+          <t>https://m.place.naver.com/place/1206099126</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,24 +952,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>매드볼릭 PT 헬스장 송도</t>
+          <t>피지오스튜디오 필라테스 &amp; PT 송도점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>madbolic-songdo@naver.com</t>
+          <t>physiostudio2021@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1352-6741</t>
+          <t>0507-1356-5739</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46104</t>
+          <t>https://talk.naver.com/ct/wual9v3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>577</v>
+        <v>53</v>
       </c>
       <c r="Q6" t="n">
-        <v>1328</v>
+        <v>563</v>
       </c>
       <c r="R6" t="n">
-        <v>1905</v>
+        <v>616</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1206099126</t>
+          <t>2019067639</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206099126</t>
+          <t>https://m.place.naver.com/place/2019067639</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,24 +1050,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>하이어짐PT 송도점</t>
+          <t>히든핏 PT&amp;헬스 송도점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>highsongdo@naver.com</t>
+          <t>hiddenfit__@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1474-8260</t>
+          <t>0507-1349-9712</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 110 은진프라자 2층 하이어짐PT 송도점</t>
+          <t>인천광역시 연수구 송도과학로28번길 50 더샵 송도트리플타워west동 2층 219~221호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4a4xp</t>
+          <t>https://talk.naver.com/ct/w7i3g95</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="Q7" t="n">
-        <v>1324</v>
+        <v>569</v>
       </c>
       <c r="R7" t="n">
-        <v>1494</v>
+        <v>749</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1642474825</t>
+          <t>1355031564</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1642474825</t>
+          <t>https://m.place.naver.com/place/1355031564</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>라프그라운드PT 송도점</t>
+          <t>더피티짐 프리미엄 더테라스점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lfitness2@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1461-8028</t>
+          <t>0507-1307-1061</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 601호</t>
+          <t>인천광역시 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://lafground.com/</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,18 +1185,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5icxb</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>668</v>
       </c>
       <c r="R8" t="n">
-        <v>97</v>
+        <v>714</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1488275180</t>
+          <t>1296216271</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488275180</t>
+          <t>https://m.place.naver.com/place/1296216271</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,39 +1241,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>무포스 PT FT 송도점</t>
+          <t>팀윤짐 PT 송도7호점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>moveforstrength@naver.com</t>
+          <t>teamyoon_7@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1406-4500</t>
+          <t>0507-1487-9688</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 2층 226호</t>
+          <t>인천광역시 연수구 신송로 161 더하이츠 5층 507호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.moveforstrength.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5x24z</t>
+          <t>https://talk.naver.com/ct/w4l4no</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>115</v>
+        <v>567</v>
       </c>
       <c r="Q9" t="n">
-        <v>645</v>
+        <v>1310</v>
       </c>
       <c r="R9" t="n">
-        <v>760</v>
+        <v>1877</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1426191152</t>
+          <t>1876943780</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426191152</t>
+          <t>https://m.place.naver.com/place/1876943780</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,34 +1344,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FWC스포츠센터</t>
+          <t>코어앤모어 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fwcsports@naver.com</t>
+          <t>coreandmore@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1360-7005</t>
+          <t>0507-1319-5328</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 107 G동 상가 2, 3층</t>
+          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.fwcsongdo.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4qg2m</t>
+          <t>https://talk.naver.com/ct/wmzjpfy</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="n">
-        <v>643</v>
+        <v>111</v>
       </c>
       <c r="R10" t="n">
-        <v>851</v>
+        <v>191</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>34249321</t>
+          <t>2021439008</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34249321</t>
+          <t>https://m.place.naver.com/place/2021439008</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>키필라테스 청라점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>resort_6@naver.com</t>
+          <t>keypilates@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>1555-7745</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
+          <t>https://talk.naver.com/ct/wyozl7z</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1386</v>
+        <v>15</v>
       </c>
       <c r="Q2" t="n">
-        <v>938</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>2324</v>
+        <v>34</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>2074412271</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>317</v>
+        <v>1387</v>
       </c>
       <c r="Q3" t="n">
-        <v>1938</v>
+        <v>937</v>
       </c>
       <c r="R3" t="n">
-        <v>2255</v>
+        <v>2324</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피트니스 연구소 송도점 헬스PT</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lfitness2@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1468-2286</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,22 +793,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pxzz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1581</v>
+        <v>317</v>
       </c>
       <c r="Q4" t="n">
-        <v>732</v>
+        <v>1938</v>
       </c>
       <c r="R4" t="n">
-        <v>2313</v>
+        <v>2255</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1806077033</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806077033</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -854,59 +850,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>매드볼릭 PT 헬스장 송도</t>
+          <t>피트니스 연구소 송도점 헬스PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>madbolic-songdo@naver.com</t>
+          <t>fitnessinssongdo@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1352-6741</t>
+          <t>0507-1468-2286</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46104</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>578</v>
+        <v>1581</v>
       </c>
       <c r="Q5" t="n">
-        <v>1334</v>
+        <v>732</v>
       </c>
       <c r="R5" t="n">
-        <v>1912</v>
+        <v>2313</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1206099126</t>
+          <t>1806077033</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206099126</t>
+          <t>https://m.place.naver.com/place/1806077033</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -952,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 송도점</t>
+          <t>매드볼릭 PT 헬스장 송도</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>physiostudio2021@naver.com</t>
+          <t>madbolic-songdo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1356-5739</t>
+          <t>0507-1352-6741</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
+          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/madbolic-songdo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,24 +976,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wual9v3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>53</v>
+        <v>578</v>
       </c>
       <c r="Q6" t="n">
-        <v>563</v>
+        <v>1335</v>
       </c>
       <c r="R6" t="n">
-        <v>616</v>
+        <v>1913</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2019067639</t>
+          <t>1206099126</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2019067639</t>
+          <t>https://m.place.naver.com/place/1206099126</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>히든핏 PT&amp;헬스 송도점</t>
+          <t>피지오스튜디오 필라테스 &amp; PT 송도점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hiddenfit__@naver.com</t>
+          <t>physiostudio_7@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1349-9712</t>
+          <t>0507-1356-5739</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로28번길 50 더샵 송도트리플타워west동 2층 219~221호</t>
+          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/physiostudio_7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,24 +1070,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7i3g95</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>180</v>
+        <v>53</v>
       </c>
       <c r="Q7" t="n">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="R7" t="n">
-        <v>749</v>
+        <v>616</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1355031564</t>
+          <t>2019067639</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1355031564</t>
+          <t>https://m.place.naver.com/place/2019067639</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1137,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>gktk1877@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1165,7 +1149,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
+          <t>인천 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1212,10 +1196,10 @@
         <v>46</v>
       </c>
       <c r="Q8" t="n">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="R8" t="n">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1234,7 +1218,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>팀윤짐 PT 송도7호점</t>
+          <t>코어앤모어 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>teamyoon_7@naver.com</t>
+          <t>coreandmore@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1487-9688</t>
+          <t>0507-1319-5328</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 161 더하이츠 5층 507호</t>
+          <t>인천 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,7 +1262,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1293,7 +1277,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4l4no</t>
+          <t>https://talk.naver.com/ct/wmzjpfy</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>567</v>
+        <v>80</v>
       </c>
       <c r="Q9" t="n">
-        <v>1310</v>
+        <v>111</v>
       </c>
       <c r="R9" t="n">
-        <v>1877</v>
+        <v>191</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1306,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1876943780</t>
+          <t>2021439008</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1876943780</t>
+          <t>https://m.place.naver.com/place/2021439008</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1344,44 +1328,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코어앤모어 PT</t>
+          <t>모베레 메디컬트레이닝 전문센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>coreandmore@naver.com</t>
+          <t>inhapac@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1319-5328</t>
+          <t>0507-1343-3540</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+          <t>인천 연수구 해돋이로 165 703호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://moverefitness.p-e.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1375,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmzjpfy</t>
+          <t>https://talk.naver.com/ct/wcbaxw</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="Q10" t="n">
-        <v>111</v>
+        <v>485</v>
       </c>
       <c r="R10" t="n">
-        <v>191</v>
+        <v>576</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1404,115 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2021439008</t>
+          <t>38547816</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021439008</t>
+          <t>https://m.place.naver.com/place/38547816</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>리버스바디</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>reverse-gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1414-6778</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>인천 연수구 송도과학로27번길 55 3층 302, 303호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/reverse-gym</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcboks</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>386</v>
+      </c>
+      <c r="R11" t="n">
+        <v>583</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>37928664</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37928664</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/송도_PT.xlsx
+++ b/naver-place-crawler/results_health/송도_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>키필라테스 청라점</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>keypilates@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1555-7745</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
+          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/keypilates.kr</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wyozl7z</t>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>15</v>
+        <v>1387</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>937</v>
       </c>
       <c r="R2" t="n">
-        <v>34</v>
+        <v>2324</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2074412271</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074412271</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>키필라테스 청라점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>keypilates@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>1555-7745</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 서구 청라커낼로288번길 10 4층 408호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>https://www.instagram.com/keypilates.kr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyozl7z</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1387</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
-        <v>937</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>2324</v>
+        <v>34</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>2074412271</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/2074412271</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -773,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mk22</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -867,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
+          <t>인천 연수구 해돋이로 168-2 6층 피트니스 연구소 송도점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -892,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pxzz</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -961,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+          <t>인천 연수구 테크노파크로111번길 11 시카고타워 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46104</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1004,10 +1020,10 @@
         <v>578</v>
       </c>
       <c r="Q6" t="n">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="R6" t="n">
-        <v>1913</v>
+        <v>1916</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1055,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
+          <t>인천 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1080,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wual9v3</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1098,10 +1118,10 @@
         <v>53</v>
       </c>
       <c r="Q7" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="R7" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1132,34 +1152,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 더테라스점</t>
+          <t>히든핏 PT&amp;헬스 송도점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gktk1877@naver.com</t>
+          <t>hiddenfit__@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1307-1061</t>
+          <t>0507-1349-9712</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
+          <t>인천 연수구 송도과학로28번길 50 더샵 송도트리플타워west동 2층 219~221호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>https://blog.naver.com/hiddenfit__</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1169,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1179,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5icxb</t>
+          <t>https://talk.naver.com/ct/w7i3g95</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1193,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="Q8" t="n">
-        <v>671</v>
+        <v>568</v>
       </c>
       <c r="R8" t="n">
-        <v>717</v>
+        <v>748</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1296216271</t>
+          <t>1355031564</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296216271</t>
+          <t>https://m.place.naver.com/place/1355031564</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1225,49 +1245,49 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코어앤모어 PT</t>
+          <t>무포스 PT FT 송도점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>coreandmore@naver.com</t>
+          <t>moveforstrength@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1319-5328</t>
+          <t>0507-1406-4500</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 연수구 하모니로178번길 22 Gtx센트럴빌딩 C동 7층 711호</t>
+          <t>인천 연수구 인천타워대로197번길 16 2층 226호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coreandmore_pt_pilates</t>
+          <t>https://www.moveforstrength.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1277,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmzjpfy</t>
+          <t>https://talk.naver.com/ct/w5x24z</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1291,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="Q9" t="n">
-        <v>111</v>
+        <v>645</v>
       </c>
       <c r="R9" t="n">
-        <v>191</v>
+        <v>760</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2021439008</t>
+          <t>1426191152</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021439008</t>
+          <t>https://m.place.naver.com/place/1426191152</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1328,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모베레 메디컬트레이닝 전문센터</t>
+          <t>더피티짐 프리미엄 더테라스점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>inhapac@naver.com</t>
+          <t>gktk1877@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1343-3540</t>
+          <t>0507-1307-1061</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 165 703호</t>
+          <t>인천 연수구 센트럴로 415 판매시설동 2층 212~214호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://moverefitness.p-e.kr/</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1365,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1375,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcbaxw</t>
+          <t>https://talk.naver.com/ct/w5icxb</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1389,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="Q10" t="n">
-        <v>485</v>
+        <v>673</v>
       </c>
       <c r="R10" t="n">
-        <v>576</v>
+        <v>719</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,113 +1424,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38547816</t>
+          <t>1296216271</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38547816</t>
+          <t>https://m.place.naver.com/place/1296216271</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>리버스바디</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>reverse-gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1414-6778</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>인천 연수구 송도과학로27번길 55 3층 302, 303호</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/reverse-gym</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcboks</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>197</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>386</v>
-      </c>
-      <c r="R11" t="n">
-        <v>583</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>37928664</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/37928664</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
